--- a/indexes/nc_build_all/lib_court_to_type.xlsx
+++ b/indexes/nc_build_all/lib_court_to_type.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\maximilien\adresse\magisnc-dinum-api-adresses-f752eef9c72d\magisnc-dinum-api-adresses-f752eef9c72d\indexes\nc_build_all\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BAPA\projets\DINUM\2025_API_ADRESSE\code\magis-dinum-api-adresses\indexes\nc_build_all\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B55179E2-18DD-4FE7-8C13-8407BEDCC6C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CB4CCC6-F46B-4476-A1B4-C88782E9F386}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4005" yWindow="2655" windowWidth="21600" windowHeight="11385" xr2:uid="{C90BA10A-D27C-4708-98FD-81C240703D2B}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C90BA10A-D27C-4708-98FD-81C240703D2B}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -31,12 +31,15 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1610" uniqueCount="934">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1612" uniqueCount="935">
   <si>
     <t>AdmComm</t>
   </si>
@@ -2838,6 +2841,9 @@
   </si>
   <si>
     <t>Agence Technique Enercal</t>
+  </si>
+  <si>
+    <t>Tribu</t>
   </si>
 </sst>
 </file>
@@ -3209,7 +3215,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB5EBE62-B84B-46F6-B096-23AFEAFFB237}">
-  <dimension ref="A1:B805"/>
+  <dimension ref="A1:B806"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -9398,31 +9404,31 @@
     </row>
     <row r="774" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A774" t="s">
-        <v>904</v>
+        <v>934</v>
       </c>
       <c r="B774" t="s">
-        <v>173</v>
+        <v>934</v>
       </c>
     </row>
     <row r="775" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A775" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="B775" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
     </row>
     <row r="776" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A776" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B776" t="s">
-        <v>68</v>
+        <v>184</v>
       </c>
     </row>
     <row r="777" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A777" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="B777" t="s">
         <v>68</v>
@@ -9430,7 +9436,7 @@
     </row>
     <row r="778" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A778" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="B778" t="s">
         <v>68</v>
@@ -9438,47 +9444,47 @@
     </row>
     <row r="779" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A779" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="B779" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="780" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A780" t="s">
-        <v>183</v>
+        <v>909</v>
       </c>
       <c r="B780" t="s">
-        <v>182</v>
+        <v>69</v>
       </c>
     </row>
     <row r="781" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A781" t="s">
-        <v>910</v>
+        <v>183</v>
       </c>
       <c r="B781" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="782" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A782" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="B782" t="s">
-        <v>83</v>
+        <v>184</v>
       </c>
     </row>
     <row r="783" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A783" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="B783" t="s">
-        <v>184</v>
+        <v>83</v>
       </c>
     </row>
     <row r="784" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A784" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="B784" t="s">
         <v>184</v>
@@ -9486,7 +9492,7 @@
     </row>
     <row r="785" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A785" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="B785" t="s">
         <v>184</v>
@@ -9494,7 +9500,7 @@
     </row>
     <row r="786" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A786" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B786" t="s">
         <v>184</v>
@@ -9502,39 +9508,39 @@
     </row>
     <row r="787" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A787" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="B787" t="s">
-        <v>83</v>
+        <v>184</v>
       </c>
     </row>
     <row r="788" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A788" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="B788" t="s">
-        <v>185</v>
+        <v>83</v>
       </c>
     </row>
     <row r="789" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A789" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="B789" t="s">
-        <v>13</v>
+        <v>185</v>
       </c>
     </row>
     <row r="790" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A790" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="B790" t="s">
-        <v>72</v>
+        <v>13</v>
       </c>
     </row>
     <row r="791" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A791" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="B791" t="s">
         <v>72</v>
@@ -9542,23 +9548,23 @@
     </row>
     <row r="792" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A792" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="B792" t="s">
-        <v>226</v>
+        <v>72</v>
       </c>
     </row>
     <row r="793" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A793" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="B793" t="s">
-        <v>2</v>
+        <v>226</v>
       </c>
     </row>
     <row r="794" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A794" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="B794" t="s">
         <v>2</v>
@@ -9566,7 +9572,7 @@
     </row>
     <row r="795" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A795" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="B795" t="s">
         <v>2</v>
@@ -9574,81 +9580,89 @@
     </row>
     <row r="796" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A796" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B796" t="s">
-        <v>60</v>
+        <v>2</v>
       </c>
     </row>
     <row r="797" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A797" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B797" t="s">
-        <v>226</v>
+        <v>60</v>
       </c>
     </row>
     <row r="798" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A798" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="B798" t="s">
-        <v>14</v>
+        <v>226</v>
       </c>
     </row>
     <row r="799" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A799" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="B799" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
     </row>
     <row r="800" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A800" t="s">
-        <v>187</v>
+        <v>928</v>
       </c>
       <c r="B800" t="s">
-        <v>186</v>
+        <v>58</v>
       </c>
     </row>
     <row r="801" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A801" t="s">
-        <v>929</v>
+        <v>187</v>
       </c>
       <c r="B801" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="802" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A802" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="B802" t="s">
-        <v>155</v>
+        <v>188</v>
       </c>
     </row>
     <row r="803" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A803" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="B803" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
     </row>
     <row r="804" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A804" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="B804" t="s">
-        <v>63</v>
+        <v>166</v>
       </c>
     </row>
     <row r="805" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A805" t="s">
+        <v>932</v>
+      </c>
+      <c r="B805" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="806" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A806" t="s">
         <v>933</v>
       </c>
-      <c r="B805" t="s">
+      <c r="B806" t="s">
         <v>83</v>
       </c>
     </row>
